--- a/J30/Australia_Impact/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Australia_Impact/Output_files/ASN_Creation_Report.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0508314880</t>
+          <t>0508312890</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081083120260000001</t>
+          <t>00081083120260000007</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0508314880</t>
+          <t>0508312890</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081083120260000002</t>
+          <t>00081083120260000008</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/J30/Australia_Impact/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Australia_Impact/Output_files/ASN_Creation_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0508312890</t>
+          <t>0509014110</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081083120260000007</t>
+          <t>00081090120260000091</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0508312890</t>
+          <t>0509014110</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081083120260000008</t>
+          <t>00081090120260000092</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -545,6 +545,1126 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00081090120260000093</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00081090120260000094</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00081090120260000095</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00081090120260000096</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00081090120260000097</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00081090120260000098</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00081090120260000099</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00081090120260000100</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00081090120260000101</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00081090120260000102</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00081090120260000103</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00081090120260000104</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00081090120260000105</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00081090120260000106</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00081090120260000107</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00081090120260000108</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00081090120260000109</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00081090120260000110</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00081090120260000111</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00081090120260000112</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00081090120260000113</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00081090120260000114</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00081090120260000115</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00081090120260000116</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>6</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00081090120260000117</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>6</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00081090120260000118</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00081090120260000119</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>AUPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0509014110</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00081090120260000120</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>727325-010-L</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0005005401</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>AUPU</t>
         </is>

--- a/J30/Australia_Impact/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Australia_Impact/Output_files/ASN_Creation_Report.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00081090120260000091</t>
+          <t>00081090220260000091</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00081090120260000092</t>
+          <t>00081090220260000092</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00081090120260000093</t>
+          <t>00081090220260000093</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00081090120260000094</t>
+          <t>00081090220260000094</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00081090120260000095</t>
+          <t>00081090220260000095</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00081090120260000096</t>
+          <t>00081090220260000096</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00081090120260000097</t>
+          <t>00081090220260000097</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00081090120260000098</t>
+          <t>00081090220260000098</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00081090120260000099</t>
+          <t>00081090220260000099</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00081090120260000100</t>
+          <t>00081090220260000100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00081090120260000101</t>
+          <t>00081090220260000101</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00081090120260000102</t>
+          <t>00081090220260000102</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>00081090120260000103</t>
+          <t>00081090220260000103</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>00081090120260000104</t>
+          <t>00081090220260000104</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>00081090120260000105</t>
+          <t>00081090220260000105</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>00081090120260000106</t>
+          <t>00081090220260000106</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>00081090120260000107</t>
+          <t>00081090220260000107</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>00081090120260000108</t>
+          <t>00081090220260000108</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>00081090120260000109</t>
+          <t>00081090220260000109</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>00081090120260000110</t>
+          <t>00081090220260000110</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>00081090120260000111</t>
+          <t>00081090220260000111</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>00081090120260000112</t>
+          <t>00081090220260000112</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>00081090120260000113</t>
+          <t>00081090220260000113</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>00081090120260000114</t>
+          <t>00081090220260000114</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>00081090120260000115</t>
+          <t>00081090220260000115</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>00081090120260000116</t>
+          <t>00081090220260000116</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>00081090120260000117</t>
+          <t>00081090220260000117</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>00081090120260000118</t>
+          <t>00081090220260000118</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>00081090120260000119</t>
+          <t>00081090220260000119</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0509014110</t>
+          <t>0509026600</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>00081090120260000120</t>
+          <t>00081090220260000120</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">

--- a/J30/Australia_Impact/Output_files/ASN_Creation_Report.xlsx
+++ b/J30/Australia_Impact/Output_files/ASN_Creation_Report.xlsx
@@ -1,43 +1,205 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="54">
+  <si>
+    <t>PLANT</t>
+  </si>
+  <si>
+    <t>ENVN</t>
+  </si>
+  <si>
+    <t>ASN_ID</t>
+  </si>
+  <si>
+    <t>LPN_ID</t>
+  </si>
+  <si>
+    <t>ITEM_ID</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>O_FACILITY</t>
+  </si>
+  <si>
+    <t>CARRIER</t>
+  </si>
+  <si>
+    <t>1093</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>0509042602</t>
+  </si>
+  <si>
+    <t>00081090420260000105</t>
+  </si>
+  <si>
+    <t>00081090420260000106</t>
+  </si>
+  <si>
+    <t>00081090420260000107</t>
+  </si>
+  <si>
+    <t>00081090420260000108</t>
+  </si>
+  <si>
+    <t>00081090420260000109</t>
+  </si>
+  <si>
+    <t>00081090420260000110</t>
+  </si>
+  <si>
+    <t>00081090420260000111</t>
+  </si>
+  <si>
+    <t>00081090420260000112</t>
+  </si>
+  <si>
+    <t>00081090420260000113</t>
+  </si>
+  <si>
+    <t>00081090420260000114</t>
+  </si>
+  <si>
+    <t>00081090420260000115</t>
+  </si>
+  <si>
+    <t>00081090420260000116</t>
+  </si>
+  <si>
+    <t>00081090420260000117</t>
+  </si>
+  <si>
+    <t>00081090420260000118</t>
+  </si>
+  <si>
+    <t>00081090420260000119</t>
+  </si>
+  <si>
+    <t>00081090420260000120</t>
+  </si>
+  <si>
+    <t>00081090420260000121</t>
+  </si>
+  <si>
+    <t>00081090420260000122</t>
+  </si>
+  <si>
+    <t>00081090420260000123</t>
+  </si>
+  <si>
+    <t>00081090420260000124</t>
+  </si>
+  <si>
+    <t>00081090420260000125</t>
+  </si>
+  <si>
+    <t>00081090420260000126</t>
+  </si>
+  <si>
+    <t>00081090420260000127</t>
+  </si>
+  <si>
+    <t>00081090420260000128</t>
+  </si>
+  <si>
+    <t>00081090420260000129</t>
+  </si>
+  <si>
+    <t>00081090420260000130</t>
+  </si>
+  <si>
+    <t>00081090420260000131</t>
+  </si>
+  <si>
+    <t>00081090420260000132</t>
+  </si>
+  <si>
+    <t>00081090420260000133</t>
+  </si>
+  <si>
+    <t>00081090420260000134</t>
+  </si>
+  <si>
+    <t>00081090420260000135</t>
+  </si>
+  <si>
+    <t>00081090420260000136</t>
+  </si>
+  <si>
+    <t>00081090420260000137</t>
+  </si>
+  <si>
+    <t>00081090420260000138</t>
+  </si>
+  <si>
+    <t>00081090420260000139</t>
+  </si>
+  <si>
+    <t>00081090420260000140</t>
+  </si>
+  <si>
+    <t>00081090420260000141</t>
+  </si>
+  <si>
+    <t>00081090420260000142</t>
+  </si>
+  <si>
+    <t>00081090420260000143</t>
+  </si>
+  <si>
+    <t>00081090420260000144</t>
+  </si>
+  <si>
+    <t>727325-010-L</t>
+  </si>
+  <si>
+    <t>0005005401</t>
+  </si>
+  <si>
+    <t>AUPU</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,94 +207,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,137 +506,1077 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PLANT</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ENVN</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ASN_ID</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LPN_ID</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ITEM_ID</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>QTY</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>O_FACILITY</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>CARRIER</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1093</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0509038070</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>00081090320260000007</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>727325-010-L</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1093</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0509038070</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>00081090320260000008</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>727325-010-L</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0005005401</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>AUPU</t>
-        </is>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10">
+        <v>6</v>
+      </c>
+      <c r="G10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11">
+        <v>6</v>
+      </c>
+      <c r="G11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12">
+        <v>6</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13">
+        <v>6</v>
+      </c>
+      <c r="G13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14">
+        <v>6</v>
+      </c>
+      <c r="G14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15">
+        <v>6</v>
+      </c>
+      <c r="G15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16">
+        <v>6</v>
+      </c>
+      <c r="G16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17">
+        <v>6</v>
+      </c>
+      <c r="G17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18">
+        <v>6</v>
+      </c>
+      <c r="G18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19">
+        <v>6</v>
+      </c>
+      <c r="G19" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20">
+        <v>6</v>
+      </c>
+      <c r="G20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21">
+        <v>6</v>
+      </c>
+      <c r="G21" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22">
+        <v>6</v>
+      </c>
+      <c r="G22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23">
+        <v>6</v>
+      </c>
+      <c r="G23" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24">
+        <v>6</v>
+      </c>
+      <c r="G24" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25">
+        <v>6</v>
+      </c>
+      <c r="G25" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26">
+        <v>6</v>
+      </c>
+      <c r="G26" t="s">
+        <v>52</v>
+      </c>
+      <c r="H26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27">
+        <v>6</v>
+      </c>
+      <c r="G27" t="s">
+        <v>52</v>
+      </c>
+      <c r="H27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" t="s">
+        <v>51</v>
+      </c>
+      <c r="F28">
+        <v>6</v>
+      </c>
+      <c r="G28" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29">
+        <v>6</v>
+      </c>
+      <c r="G29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F30">
+        <v>6</v>
+      </c>
+      <c r="G30" t="s">
+        <v>52</v>
+      </c>
+      <c r="H30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31">
+        <v>6</v>
+      </c>
+      <c r="G31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32">
+        <v>6</v>
+      </c>
+      <c r="G32" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33">
+        <v>6</v>
+      </c>
+      <c r="G33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" t="s">
+        <v>51</v>
+      </c>
+      <c r="F34">
+        <v>6</v>
+      </c>
+      <c r="G34" t="s">
+        <v>52</v>
+      </c>
+      <c r="H34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35">
+        <v>6</v>
+      </c>
+      <c r="G35" t="s">
+        <v>52</v>
+      </c>
+      <c r="H35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" t="s">
+        <v>51</v>
+      </c>
+      <c r="F36">
+        <v>6</v>
+      </c>
+      <c r="G36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F37">
+        <v>6</v>
+      </c>
+      <c r="G37" t="s">
+        <v>52</v>
+      </c>
+      <c r="H37" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" t="s">
+        <v>51</v>
+      </c>
+      <c r="F38">
+        <v>6</v>
+      </c>
+      <c r="G38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H38" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" t="s">
+        <v>51</v>
+      </c>
+      <c r="F39">
+        <v>6</v>
+      </c>
+      <c r="G39" t="s">
+        <v>52</v>
+      </c>
+      <c r="H39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" t="s">
+        <v>51</v>
+      </c>
+      <c r="F40">
+        <v>6</v>
+      </c>
+      <c r="G40" t="s">
+        <v>52</v>
+      </c>
+      <c r="H40" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" t="s">
+        <v>51</v>
+      </c>
+      <c r="F41">
+        <v>6</v>
+      </c>
+      <c r="G41" t="s">
+        <v>52</v>
+      </c>
+      <c r="H41" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>